--- a/public/templates/universitet-guideline-shablon.xlsx
+++ b/public/templates/universitet-guideline-shablon.xlsx
@@ -280,9 +280,9 @@
     </comment>
     <comment ref="I1" authorId="0" shapeId="0">
       <text>
-        <t>Qabul darajasi. transfer = 편입학, til_kursi = 어학당.
+        <t>Qabul darajasi. transfer = 편입학, til_kursi = 어학당, kasbiy = kasbiy ta'lim (전문대학, 전문학사).
 Turi: tanlov
-Qiymatlar: bakalavr, transfer, magistratura, doktorantura, til_kursi
+Qiymatlar: bakalavr, transfer, magistratura, doktorantura, til_kursi, kasbiy
 Namuna: bakalavr</t>
       </text>
     </comment>
@@ -1406,8 +1406,8 @@
     <dataValidation sqref="H2" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Noto'g'ri qiymat" error="Faqat: bahor, kuz" type="list">
       <formula1>"bahor,kuz"</formula1>
     </dataValidation>
-    <dataValidation sqref="I2" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Noto'g'ri qiymat" error="Faqat: bakalavr, transfer, magistratura, doktorantura, til_kursi" type="list">
-      <formula1>"bakalavr,transfer,magistratura,doktorantura,til_kursi"</formula1>
+    <dataValidation sqref="I2" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Noto'g'ri qiymat" error="Faqat: bakalavr, transfer, magistratura, doktorantura, til_kursi, kasbiy" type="list">
+      <formula1>"bakalavr,transfer,magistratura,doktorantura,til_kursi,kasbiy"</formula1>
     </dataValidation>
     <dataValidation sqref="N2" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Noto'g'ri qiymat" error="Faqat: KRW, USD" type="list">
       <formula1>"KRW,USD"</formula1>
@@ -2345,7 +2345,7 @@
       </c>
       <c r="D44" s="14" t="inlineStr">
         <is>
-          <t>bakalavr, transfer, magistratura, doktorantura, til_kursi</t>
+          <t>bakalavr, transfer, magistratura, doktorantura, til_kursi, kasbiy</t>
         </is>
       </c>
       <c r="E44" s="14" t="inlineStr">
@@ -2355,7 +2355,7 @@
       </c>
       <c r="F44" s="14" t="inlineStr">
         <is>
-          <t>Qabul darajasi. transfer = 편입학, til_kursi = 어학당.</t>
+          <t>Qabul darajasi. transfer = 편입학, til_kursi = 어학당, kasbiy = kasbiy ta'lim (전문대학, 전문학사).</t>
         </is>
       </c>
     </row>

--- a/public/templates/universitet-guideline-shablon.xlsx
+++ b/public/templates/universitet-guideline-shablon.xlsx
@@ -272,15 +272,15 @@
     </comment>
     <comment ref="H1" authorId="0" shapeId="0">
       <text>
-        <t>bahor = mart qabuli (1학기 / 전기), kuz = sentabr qabuli (2학기 / 후기). Guideline sarlavhasidan tasdiqlanadi.
+        <t>bahor = mart qabuli (1학기 / 전기), kuz = sentabr qabuli (2학기 / 후기). Til kursida yana: yoz = iyun termi (여름학기), qish = dekabr termi (겨울학기) — faqat daraja = til_kursi bo'lsa. Guideline sarlavhasidan tasdiqlanadi.
 Turi: tanlov
-Qiymatlar: bahor, kuz
+Qiymatlar: bahor, yoz, kuz, qish
 Namuna: bahor</t>
       </text>
     </comment>
     <comment ref="I1" authorId="0" shapeId="0">
       <text>
-        <t>Qabul darajasi. transfer = 편입학, til_kursi = 어학당, kasbiy = kasbiy ta'lim (전문대학, 전문학사).
+        <t>Qabul darajasi. transfer = 편입학, til_kursi = til kursi (어학당, 한국어 연수과정), kasbiy = kasbiy ta'lim (전문대학, 전문학사).
 Turi: tanlov
 Qiymatlar: bakalavr, transfer, magistratura, doktorantura, til_kursi, kasbiy
 Namuna: bakalavr</t>
@@ -659,14 +659,14 @@
     </comment>
     <comment ref="E1" authorId="0" shapeId="0">
       <text>
-        <t>Fakultet / yo'nalish (학과, 전공), inglizcha.
+        <t>Fakultet / yo'nalish (학과, 전공), inglizcha. Til kursida — kurs nomi (masalan, Regular Korean Language Program).
 Turi: matn
 Namuna: Business Administration</t>
       </text>
     </comment>
     <comment ref="F1" authorId="0" shapeId="0">
       <text>
-        <t>Fakultet / yo'nalish (학과, 전공), koreyscha.
+        <t>Fakultet / yo'nalish (학과, 전공), koreyscha. Til kursida — kurs nomi (masalan, 정규과정).
 Turi: matn
 Namuna: 경영학과</t>
       </text>
@@ -1403,8 +1403,8 @@
   </sheetData>
   <autoFilter ref="A1:AO2"/>
   <dataValidations count="13">
-    <dataValidation sqref="H2" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Noto'g'ri qiymat" error="Faqat: bahor, kuz" type="list">
-      <formula1>"bahor,kuz"</formula1>
+    <dataValidation sqref="H2" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Noto'g'ri qiymat" error="Faqat: bahor, yoz, kuz, qish" type="list">
+      <formula1>"bahor,yoz,kuz,qish"</formula1>
     </dataValidation>
     <dataValidation sqref="I2" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Noto'g'ri qiymat" error="Faqat: bakalavr, transfer, magistratura, doktorantura, til_kursi, kasbiy" type="list">
       <formula1>"bakalavr,transfer,magistratura,doktorantura,til_kursi,kasbiy"</formula1>
@@ -1885,7 +1885,7 @@
     <row r="11">
       <c r="A11" s="6" t="inlineStr">
         <is>
-          <t>8. Bitta fayl = bitta guideline_id. Bitta PDF'da bir nechta daraja bo'lsa (masalan, bakalavr va transfer) — har biriga alohida fayl.</t>
+          <t>8. Bitta fayl = bitta guideline_id. Bitta PDF'da bir nechta daraja bo'lsa (masalan, bakalavr va transfer) — har biriga alohida fayl. Til kursida har bir term (bahor, yoz, kuz, qish) — alohida fayl.</t>
         </is>
       </c>
     </row>
@@ -2313,7 +2313,7 @@
       </c>
       <c r="D43" s="14" t="inlineStr">
         <is>
-          <t>bahor, kuz</t>
+          <t>bahor, yoz, kuz, qish</t>
         </is>
       </c>
       <c r="E43" s="14" t="inlineStr">
@@ -2323,7 +2323,7 @@
       </c>
       <c r="F43" s="14" t="inlineStr">
         <is>
-          <t>bahor = mart qabuli (1학기 / 전기), kuz = sentabr qabuli (2학기 / 후기). Guideline sarlavhasidan tasdiqlanadi.</t>
+          <t>bahor = mart qabuli (1학기 / 전기), kuz = sentabr qabuli (2학기 / 후기). Til kursida yana: yoz = iyun termi (여름학기), qish = dekabr termi (겨울학기) — faqat daraja = til_kursi bo'lsa. Guideline sarlavhasidan tasdiqlanadi.</t>
         </is>
       </c>
     </row>
@@ -2355,7 +2355,7 @@
       </c>
       <c r="F44" s="14" t="inlineStr">
         <is>
-          <t>Qabul darajasi. transfer = 편입학, til_kursi = 어학당, kasbiy = kasbiy ta'lim (전문대학, 전문학사).</t>
+          <t>Qabul darajasi. transfer = 편입학, til_kursi = til kursi (어학당, 한국어 연수과정), kasbiy = kasbiy ta'lim (전문대학, 전문학사).</t>
         </is>
       </c>
     </row>
@@ -3787,7 +3787,7 @@
       </c>
       <c r="F92" s="14" t="inlineStr">
         <is>
-          <t>Fakultet / yo'nalish (학과, 전공), inglizcha.</t>
+          <t>Fakultet / yo'nalish (학과, 전공), inglizcha. Til kursida — kurs nomi (masalan, Regular Korean Language Program).</t>
         </is>
       </c>
     </row>
@@ -3815,7 +3815,7 @@
       </c>
       <c r="F93" s="14" t="inlineStr">
         <is>
-          <t>Fakultet / yo'nalish (학과, 전공), koreyscha.</t>
+          <t>Fakultet / yo'nalish (학과, 전공), koreyscha. Til kursida — kurs nomi (masalan, 정규과정).</t>
         </is>
       </c>
     </row>
